--- a/统计信息.xlsx
+++ b/统计信息.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\OpenHanako\SUAT-cats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9431BD1F-6C9C-4692-99C6-E1D690ED0D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F12AFAB-81DC-48D4-8FE6-75969B93F2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="185">
   <si>
     <t>编号</t>
   </si>
@@ -411,18 +411,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>一只普通的怕人狸花，看起来比较壮实，嘴巴比较白</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>一只普通的亲人狸花，以前陪伴小咪长大，眼屎很多，2025年9月失踪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>一只普通的怕人狸花，古典纹，前狸花帮的一员，2026年年初失踪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>一只尝尝到处蹭饭的狸花，2026年5月出现在校门口，喜欢蹭饭，和贪吃哥是好朋猫，是个gay</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -499,10 +491,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>五小只里最喜欢哈气的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>贪吃的话痨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -547,15 +535,127 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>和古典纹猫妈一起的白猫，2026年年初失踪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大肚子怕人狸花，很像古典纹的放大版，只是左后腿多了一块纹，2026年年初失踪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪</t>
+    <t>特别潦草的三花妈，生活环境总是可以被她搞得乱七八糟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小时候是一只怎么吃也吃不胖的高精力小猫，现在是吃一点点就胖的高精力小猫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以前他还很瘦，一见人就哈气。现在发现人类是个益虫，成功完成了蜕变。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生下了橘头、头套、黑头三小只，现在越吃越胖，天天睡大觉。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三小只里最亲人的橘，从小胆子最大，可以偷偷地摸，从国家中心被救下来以后，更加的亲人。于2026.3.21凌晨在马路上回到喵星。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每天晚上都会从校外游荡过来，抢猫妈的饭吃、欺负三小只、和猫猫打架，只对古典纹好，罪大恶极。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在校园里四处游荡的古典纹，特别瘦小，人一靠近就哈气，很难养熟。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曾经住在河边桥底下的一只奶牛，像蝙蝠侠，2026年年初失踪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狸花帮的一员，生下了大约四只小猫仔，但是目前见不到任何一只崽子。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生下了五小只特别好看的小猫崽，特别怕人，一见人靠近崽子就哈气，2026.3.18傍晚在非机动车道上去世。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五小只里最霸道的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五小只里最霸道的，和他妈一样喜欢哈气，胸前有一个黑色的领结，特别霸道，特别护食。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五小只里胆子最小的，别人都在吃东西，就他在最后面。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五小只里面最好看的一只，年纪轻轻就已怀孕，已饮茶绝育。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然出现在猫妈地盘里的一只话痨，喜欢被人摸下巴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在学校里转来转去，就为了蹭一口饭吃，是猫妈的垃圾桶。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千里迢迢跟着他的干父亲头3来学校蹭饭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千里迢迢带着他的干女儿头孢来学校蹭饭，因为长得很像头套和黑头，所以取名叫头3。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三小只里面最调皮的，怎么吃也吃不胖，喜欢抢兄弟的饭吃，吃一会儿就跑出去玩，傻傻的。因为绝完育带着头套直接溜了，故取名头套。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三小只里最傲娇的，从小就不屑于亲人，但是人一来或人一走就第一个赶去欢迎。因为头在三只里面是最黑的，故取名黑头。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅仅两次出过的黑猫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特别标准的一只几把猫，和小咪草草都很要好。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然出现的一纸亲人的三花，不喜欢被人摸背和屁股。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然出现的一只长得很像希特勒，但是眼睛很好看的奶牛，和小花是情侣。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然出现的一只有橘色点点的小猫，的时候特别贪玩，但是主要还是在椅子上睡觉。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然出现的一只怕人的三花，常常过来蹭饭。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一只普通的怕人狸花，看起来比较壮实，嘴巴比较白，经常蹭饭。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一只普通的怕人小狸花，古典纹，前狸花帮的一员，2026年年初失踪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和古典纹猫妈一起的白猫，2026年年初失踪。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大肚子怕人狸花，很像古典纹的放大版，只是左后腿多了一块纹，2026年年初失踪。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -717,7 +817,7 @@
                   <c:v>普通的大橘</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪</c:v>
+                  <c:v>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪。</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1111,7 +1211,7 @@
                   <c:v>普通的大橘</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪</c:v>
+                  <c:v>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪。</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1505,7 +1605,7 @@
                   <c:v>普通的大橘</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪</c:v>
+                  <c:v>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪。</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1899,7 +1999,7 @@
                   <c:v>普通的大橘</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪</c:v>
+                  <c:v>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪。</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4866,10 +4966,10 @@
         <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>7</v>
@@ -4893,9 +4993,11 @@
         <v>119</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G3" s="1"/>
+        <v>129</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="H3" s="2" t="s">
         <v>10</v>
       </c>
@@ -4918,9 +5020,11 @@
         <v>119</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G4" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>155</v>
+      </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
       </c>
@@ -4943,9 +5047,11 @@
         <v>119</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G5" s="1"/>
+        <v>131</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>156</v>
+      </c>
       <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
@@ -4968,9 +5074,11 @@
         <v>119</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="1"/>
+        <v>132</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
       </c>
@@ -4993,9 +5101,11 @@
         <v>120</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="H7" s="2" t="s">
         <v>22</v>
       </c>
@@ -5018,9 +5128,11 @@
         <v>119</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G8" s="1"/>
+        <v>134</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="H8" s="2" t="s">
         <v>25</v>
       </c>
@@ -5043,9 +5155,11 @@
         <v>119</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G9" s="1"/>
+        <v>135</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>173</v>
+      </c>
       <c r="H9" s="2" t="s">
         <v>28</v>
       </c>
@@ -5068,9 +5182,11 @@
         <v>119</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>136</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>31</v>
       </c>
@@ -5093,9 +5209,11 @@
         <v>119</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G11" s="1"/>
+        <v>137</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>160</v>
+      </c>
       <c r="H11" s="2" t="s">
         <v>34</v>
       </c>
@@ -5118,9 +5236,11 @@
         <v>118</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G12" s="1"/>
+        <v>138</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="H12" s="2" t="s">
         <v>37</v>
       </c>
@@ -5143,9 +5263,11 @@
         <v>119</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G13" s="1"/>
+        <v>139</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>162</v>
+      </c>
       <c r="H13" s="2" t="s">
         <v>40</v>
       </c>
@@ -5168,9 +5290,11 @@
         <v>120</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G14" s="1"/>
+        <v>139</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>163</v>
+      </c>
       <c r="H14" s="2" t="s">
         <v>43</v>
       </c>
@@ -5193,9 +5317,11 @@
         <v>119</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G15" s="1"/>
+        <v>140</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="H15" s="2" t="s">
         <v>46</v>
       </c>
@@ -5218,9 +5344,11 @@
         <v>119</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G16" s="1"/>
+        <v>164</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="H16" s="2" t="s">
         <v>49</v>
       </c>
@@ -5243,9 +5371,11 @@
         <v>119</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G17" s="1"/>
+        <v>141</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>167</v>
+      </c>
       <c r="H17" s="2" t="s">
         <v>52</v>
       </c>
@@ -5268,9 +5398,11 @@
         <v>119</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G18" s="1"/>
+        <v>142</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="H18" s="2" t="s">
         <v>55</v>
       </c>
@@ -5293,9 +5425,11 @@
         <v>119</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G19" s="1"/>
+        <v>143</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="H19" s="2" t="s">
         <v>58</v>
       </c>
@@ -5318,9 +5452,11 @@
         <v>119</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G20" s="1"/>
+        <v>144</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="H20" s="2" t="s">
         <v>61</v>
       </c>
@@ -5343,9 +5479,11 @@
         <v>119</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G21" s="1"/>
+        <v>145</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="H21" s="2" t="s">
         <v>64</v>
       </c>
@@ -5368,9 +5506,11 @@
         <v>119</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G22" s="1"/>
+        <v>146</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="H22" s="2" t="s">
         <v>67</v>
       </c>
@@ -5393,9 +5533,11 @@
         <v>119</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G23" s="1"/>
+        <v>147</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="H23" s="2" t="s">
         <v>70</v>
       </c>
@@ -5418,9 +5560,11 @@
         <v>118</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G24" s="1"/>
+        <v>148</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>174</v>
+      </c>
       <c r="H24" s="2" t="s">
         <v>73</v>
       </c>
@@ -5443,9 +5587,11 @@
         <v>119</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G25" s="1"/>
+        <v>149</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="H25" s="2" t="s">
         <v>76</v>
       </c>
@@ -5468,9 +5614,11 @@
         <v>119</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G26" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="H26" s="2" t="s">
         <v>79</v>
       </c>
@@ -5493,9 +5641,11 @@
         <v>119</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G27" s="1"/>
+        <v>151</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>178</v>
+      </c>
       <c r="H27" s="2" t="s">
         <v>82</v>
       </c>
@@ -5518,9 +5668,11 @@
         <v>119</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" s="1"/>
+        <v>152</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>179</v>
+      </c>
       <c r="H28" s="2" t="s">
         <v>85</v>
       </c>
@@ -5573,7 +5725,7 @@
         <v>121</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>91</v>
@@ -5600,7 +5752,7 @@
         <v>121</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>94</v>
@@ -5627,7 +5779,7 @@
         <v>121</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>97</v>
@@ -5654,7 +5806,7 @@
         <v>121</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>100</v>
@@ -5678,10 +5830,10 @@
         <v>118</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>103</v>
@@ -5693,7 +5845,7 @@
         <v>104</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>115</v>
@@ -5708,7 +5860,7 @@
         <v>121</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>105</v>
@@ -5732,10 +5884,10 @@
         <v>118</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>108</v>
@@ -5759,10 +5911,10 @@
         <v>118</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>111</v>

--- a/统计信息.xlsx
+++ b/统计信息.xlsx
@@ -2026,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="33.55" customHeight="1"/>
   <cols>
     <col width="16.28515625" customWidth="1" style="1" min="1" max="1"/>
@@ -2078,1493 +2078,1375 @@
       <c r="I1" s="1" t="n"/>
     </row>
     <row r="2" ht="33.55" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>丑橘(暂用名)</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>lost</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>校门口超级亲人的橘</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>校门口超级亲人的橘，经常在外卖车上睡觉，有很多人喂，于2025年年中失踪，小道消息是被领养了</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>ugly_orange</t>
         </is>
       </c>
-      <c r="I2" s="1" t="n"/>
     </row>
     <row r="3" ht="33.55" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>草草</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>超级怕人的潦草三花</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>特别潦草的三花妈，生活环境总是可以被她搞得乱七八糟</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>grass_grass</t>
         </is>
       </c>
-      <c r="I3" s="1" t="n"/>
     </row>
     <row r="4" ht="33.55" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>曙小咪</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>在减肥的雀猫</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>小时候是一只怎么吃也吃不胖的高精力小猫，现在是吃一点点就胖的高精力小猫</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>shu_xiao_meow</t>
         </is>
       </c>
-      <c r="I4" s="1" t="n"/>
     </row>
     <row r="5" ht="33.55" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>奶牛哥</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>蜕变的典范</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>以前他还很瘦，一见人就哈气。现在发现人类是个益虫，成功完成了蜕变。</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>milk_cow_brother</t>
         </is>
       </c>
-      <c r="I5" s="1" t="n"/>
     </row>
     <row r="6" ht="33.55" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>猫妈</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>三小只的妈妈</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>生下了橘头、头套、黑头三小只，现在越吃越胖，天天睡大觉。</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>cat_mom</t>
         </is>
       </c>
-      <c r="I6" s="1" t="n"/>
     </row>
     <row r="7" ht="33.55" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>橘头</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>三小只里最亲人的</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>三小只里最亲人的橘，从小胆子最大，可以偷偷地摸，从国家中心被救下来以后，更加的亲人。于2026.3.21凌晨在马路上回到喵星。</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>三小只里最亲人的橘，从小胆子最大，可以偷偷地摸，从国交中心被救下来以后，更加的亲人。于2026.3.21凌晨在马路上回到喵星。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>orange_head</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n"/>
     </row>
     <row r="8" ht="33.55" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>头套</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>三小只里最皮的</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>三小只里面最调皮的，怎么吃也吃不胖，喜欢抢兄弟的饭吃，吃一会儿就跑出去玩，傻傻的。因为绝完育带着头套直接溜了，故取名头套。</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>head_tao</t>
         </is>
       </c>
-      <c r="I8" s="1" t="n"/>
     </row>
     <row r="9" ht="33.55" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>黑头</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>三小只里最高冷的</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>三小只里最傲娇的，从小就不屑于亲人，但是人一来或人一走就第一个赶去欢迎。因为头在三只里面是最黑的，故取名黑头。</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>black_head</t>
         </is>
       </c>
-      <c r="I9" s="1" t="n"/>
     </row>
     <row r="10" ht="33.55" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>老橘</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>战斗力最强的大橘</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>每天晚上都会从校外游荡过来，抢猫妈的饭吃、欺负三小只、和猫猫打架，只对古典纹好，罪大恶极。</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>big_orange_one</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="33.55" customHeight="1">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>古典纹(暂用名)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>怕人的古典纹狸花</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>狸花帮的一员，在校园里四处游荡的古典纹，特别瘦小，对大多数猫不错，但是人一靠近就哈气，养熟需要耐心。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>gu_dian_wen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="33.55" customHeight="1">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>河边奶牛(暂用名)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>蝙蝠侠</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>曾经住在河边桥底下的一只奶牛，像蝙蝠侠，2026年年初失踪</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>river_side_milk_cow</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="33.55" customHeight="1">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>简州猫妈(暂用名)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>怕人的猫妈</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>狸花帮的一员，生下了大约四只小猫仔，但是目前见不到任何一只崽子。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>jian_zhou_cat_mum</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="33.55" customHeight="1">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>奶牛猫妈</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>star</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>怕人的猫妈</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>生下了五小只特别好看的小猫崽，特别怕人，一见人靠近崽子就哈气，2026.3.18傍晚在非机动车道上去世。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>cow_cat_mom</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="33.55" customHeight="1">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>白手套口水巾(暂用名)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>五小只里胆子最大的</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>奶牛猫妈生的五小只里胆子最大的。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>white_glove_bib</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="33.55" customHeight="1">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>黑老大</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>五小只里最霸道的</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>奶牛猫妈生的五小只里最霸道的，和他妈一样喜欢哈气，胸前有一个黑色的领结，特别霸道，特别护食。</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>black_boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33.55" customHeight="1">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>五月</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>五小只里最好看的</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>奶牛猫妈生的五小只里面最好看的一只，年纪轻轻就已怀孕，已绝育。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33.55" customHeight="1">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>六月</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>五小只里胆子最小的</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>奶牛猫妈生的五小只里胆子最小的，别人都在吃东西，就他在最后面。</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33.55" customHeight="1">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>大脚橘</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>贪吃的话痨</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>突然出现在猫妈地盘里的一只话痨，喜欢被人摸下巴</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>big_foot_orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33.55" customHeight="1">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>贪吃哥</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>一直在蹭饭的路上</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>在学校里转来转去，就为了蹭一口饭吃，是猫妈的垃圾桶。</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>like_eat_brother</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33.55" customHeight="1">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>头3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>猕猴桃</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>千里迢迢带着他的干女儿头孢来学校蹭饭，因为长得很像头套和黑头，所以取名叫头3。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>head_three</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="33.55" customHeight="1">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>头孢</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>哈气就是喵喵</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>千里迢迢跟着他的“干父亲”头3来学校蹭饭，因为他是头三的“干宝宝”，所以叫头孢（宝）。比较亲人，可以偷偷地摸，但是哈气和喵喵的代码写到了一起，哈气就是喵喵，喵喵就是哈气。</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>tou_baby</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33.55" customHeight="1">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>细细条</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>渣猫</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>特别标准的一只几把猫，和小咪草草都很要好。</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>thin_stripe</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="33.55" customHeight="1">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>小黑</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>普通的玄猫</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>仅仅两次出现过的黑猫</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>small_black</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="33.55" customHeight="1">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>袁小花</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>亲人的三花</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>突然出现的一只亲人的三花，不喜欢被人摸背和屁股。</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>yuan_small_flower</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="33.55" customHeight="1">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>袁小牛</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>貌美的奶牛</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>突然出现的一只长得很像希特勒，但是眼睛很好看的奶牛，和小花是情侣。</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>yuan_small_cow</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="33.55" customHeight="1">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>点点</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>高精力和低精力并存</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>突然出现的一只有橘色点点的小猫，高精力的时候特别贪玩，萎靡不振的时候在椅子上睁着眼睛睡觉。</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>dot_dot</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="33.55" customHeight="1">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>怕人三花(暂用名)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>普通的三花</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>突然出现的一只怕人的三花，常常过来蹭饭。</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>pa_ren_san_hua</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="33.55" customHeight="1">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>狸花1号(暂用名)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>普通的狸花</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>一只普通的怕人狸花，背上有纹，有口水巾</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>li_hua_one</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="33.55" customHeight="1">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>狸花2号(暂用名)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>普通的狸花</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>一只普通的怕人狸花，看起来比较壮实，嘴巴比较白，经常蹭饭。</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>li_hua_two</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="33.55" customHeight="1">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>狸花3号(暂用名)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>普通的狸花</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>一只普通的怕人小狸花，古典纹，前狸花帮的一员，2026年年初失踪</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>li_hua_three</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="33.55" customHeight="1">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>狸花4号(暂用名)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>普通的狸花</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>一只普通的亲人狸花，以前陪伴小咪长大，眼屎很多，2025年9月失踪</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>li_hua_four</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="33.55" customHeight="1">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>狸花5号(暂用名)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>普通的狸花</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>一只尝尝到处蹭饭的狸花，2026年5月出现在校门口，喜欢蹭饭，和贪吃哥是好朋猫，是个gay</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>li_hua_five</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="33.55" customHeight="1">
+      <c r="A34" t="n">
+        <v>35</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>大橘1号(暂用名)</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>战斗力最强的大橘</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>每天晚上都会从校外游荡过来，抢猫妈的饭吃、欺负三小只、和猫猫打架，只对古典纹好，罪大恶极。</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>big_orange_one</t>
-        </is>
-      </c>
-      <c r="I10" s="1" t="n"/>
-    </row>
-    <row r="11" ht="33.55" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>古典纹(暂用名)</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>普通的大橘</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>喜欢小只古典纹，毛色偏橘，从未被古典纹喜欢过，只会被被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2026年年初失踪。</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>big_orange_two</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="33.55" customHeight="1">
+      <c r="A35" t="n">
+        <v>36</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>大橘2号（暂用名）</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>普通的大橘</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>有点偏奶油色，喜欢小只古典纹，古典纹也爱过，但是后来就被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2025年年末失踪。</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>big_orange_three</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="33.55" customHeight="1">
+      <c r="A36" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>白猫(暂用名)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>普通的白猫</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>和古典纹猫妈一起的白猫，2026年年初失踪。</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>white_cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="33.55" customHeight="1">
+      <c r="A37" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>古典纹猫妈(暂用名)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>怕人的古典纹狸花</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>在校园里四处游荡的古典纹，特别瘦小，人一靠近就哈气，很难养熟。</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>gu_dian_wen</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="n"/>
-    </row>
-    <row r="12" ht="33.55" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>河边奶牛(暂用名)</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
+      <c r="D37" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>lost</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>蝙蝠侠</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>曾经住在河边桥底下的一只奶牛，像蝙蝠侠，2026年年初失踪</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>river_side_milk_cow</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="n"/>
-    </row>
-    <row r="13" ht="33.55" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>简州猫妈(暂用名)</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>怕人的猫妈</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>狸花帮的一员，生下了大约四只小猫仔，但是目前见不到任何一只崽子。</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>jian_zhou_cat_mum</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="n"/>
-    </row>
-    <row r="14" ht="33.55" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>奶牛猫妈</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>star</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>怕人的猫妈</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>生下了五小只特别好看的小猫崽，特别怕人，一见人靠近崽子就哈气，2026.3.18傍晚在非机动车道上去世。</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>cow_cat_mom</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="n"/>
-    </row>
-    <row r="15" ht="33.55" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>白手套口水巾(暂用名)</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>五小只里胆子最大的</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>五小只里胆子最大的</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>white_glove_bib</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="33.55" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>黑老大</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>五小只里最霸道的</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>五小只里最霸道的，和他妈一样喜欢哈气，胸前有一个黑色的领结，特别霸道，特别护食。</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>black_boss</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="n"/>
-    </row>
-    <row r="17" ht="33.55" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>五月</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>好可爱的宝宝</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>五小只里面最好看的一只，年纪轻轻就已怀孕，已饮茶绝育。</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="n"/>
-    </row>
-    <row r="18" ht="33.55" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>六月</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>五小只里胆子最小的</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>五小只里胆子最小的，别人都在吃东西，就他在最后面。</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>June</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="n"/>
-    </row>
-    <row r="19" ht="33.55" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>大脚橘</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>贪吃的话痨</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>突然出现在猫妈地盘里的一只话痨，喜欢被人摸下巴</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>big_foot_orange</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="n"/>
-    </row>
-    <row r="20" ht="33.55" customHeight="1">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>贪吃哥</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>一直在蹭饭的路上</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>在学校里转来转去，就为了蹭一口饭吃，是猫妈的垃圾桶。</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>like_eat_brother</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="n"/>
-    </row>
-    <row r="21" ht="33.55" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>头3</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>猕猴桃</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>千里迢迢带着他的干女儿头孢来学校蹭饭，因为长得很像头套和黑头，所以取名叫头3。</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>head_three</t>
-        </is>
-      </c>
-      <c r="I21" s="1" t="n"/>
-    </row>
-    <row r="22" ht="33.55" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>头孢</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>哈气就是喵喵</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>千里迢迢跟着他的干父亲头3来学校蹭饭</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>tou_baby</t>
-        </is>
-      </c>
-      <c r="I22" s="1" t="n"/>
-    </row>
-    <row r="23" ht="33.55" customHeight="1">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>细条条</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>渣猫</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>特别标准的一只几把猫，和小咪草草都很要好。</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>thin_stripe</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="n"/>
-    </row>
-    <row r="24" ht="33.55" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>小黑</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>普通的玄猫</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>仅仅两次出过的黑猫</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>small_black</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="n"/>
-    </row>
-    <row r="25" ht="33.55" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>袁小花</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>亲人的三花</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>突然出现的一纸亲人的三花，不喜欢被人摸背和屁股。</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>yuan_small_flower</t>
-        </is>
-      </c>
-      <c r="I25" s="1" t="n"/>
-    </row>
-    <row r="26" ht="33.55" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>袁小牛</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>貌美的奶牛</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>突然出现的一只长得很像希特勒，但是眼睛很好看的奶牛，和小花是情侣。</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>yuan_small_cow</t>
-        </is>
-      </c>
-      <c r="I26" s="1" t="n"/>
-    </row>
-    <row r="27" ht="33.55" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>点点</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>高精力和低精力并存</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>突然出现的一只有橘色点点的小猫，的时候特别贪玩，但是主要还是在椅子上睡觉。</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>dot_dot</t>
-        </is>
-      </c>
-      <c r="I27" s="1" t="n"/>
-    </row>
-    <row r="28" ht="33.55" customHeight="1">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>怕人三花(暂用名)</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>普通的三花</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>突然出现的一只怕人的三花，常常过来蹭饭。</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>pa_ren_san_hua</t>
-        </is>
-      </c>
-      <c r="I28" s="1" t="n"/>
-    </row>
-    <row r="29" ht="33.55" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>狸花1号(暂用名)</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>普通的狸花</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>一只普通的怕人狸花，背上有纹，有口水巾</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>li_hua_one</t>
-        </is>
-      </c>
-      <c r="I29" s="1" t="n"/>
-    </row>
-    <row r="30" ht="33.55" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>狸花2号(暂用名)</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>普通的狸花</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>一只普通的怕人狸花，看起来比较壮实，嘴巴比较白，经常蹭饭。</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>li_hua_two</t>
-        </is>
-      </c>
-      <c r="I30" s="1" t="n"/>
-    </row>
-    <row r="31" ht="33.55" customHeight="1">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>狸花3号(暂用名)</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>普通的狸花</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>一只普通的怕人小狸花，古典纹，前狸花帮的一员，2026年年初失踪</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>li_hua_three</t>
-        </is>
-      </c>
-      <c r="I31" s="1" t="n"/>
-    </row>
-    <row r="32" ht="33.55" customHeight="1">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>狸花4号(暂用名)</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>普通的狸花</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>一只普通的亲人狸花，以前陪伴小咪长大，眼屎很多，2025年9月失踪</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>li_hua_four</t>
-        </is>
-      </c>
-      <c r="I32" s="1" t="n"/>
-    </row>
-    <row r="33" ht="33.55" customHeight="1">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>狸花5号(暂用名)</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>普通的狸花</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>一只尝尝到处蹭饭的狸花，2026年5月出现在校门口，喜欢蹭饭，和贪吃哥是好朋猫，是个gay</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>li_hua_five</t>
-        </is>
-      </c>
-      <c r="I33" s="1" t="n"/>
-    </row>
-    <row r="34" ht="33.55" customHeight="1">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>白猫(暂用名)</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>普通的白猫</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>和古典纹猫妈一起的白猫，2026年年初失踪。</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>white_cat</t>
-        </is>
-      </c>
-      <c r="I34" s="1" t="n"/>
-    </row>
-    <row r="35" ht="33.55" customHeight="1">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>古典纹猫妈(暂用名)</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>普通的狸花</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>大肚子怕人狸花，很像古典纹的放大版，只是左后腿多了一块纹，2026年年初失踪。</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>gu_dian_wen_cat_mom</t>
         </is>
       </c>
-      <c r="I35" s="1" t="n"/>
-    </row>
-    <row r="36" ht="33.55" customHeight="1">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>大橘2号(暂用名)</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>普通的大橘</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪。</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>big_orange_two</t>
-        </is>
-      </c>
-      <c r="I36" s="1" t="n"/>
-    </row>
-    <row r="37" ht="33.55" customHeight="1">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>大橘3号</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>普通的大橘</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>喜欢小只古典纹，但是后来见面就被古典纹哈气嫌弃，因为古典纹已经喜欢上了大橘1号，2026年年初失踪。</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>big_orange_three</t>
-        </is>
-      </c>
-      <c r="I37" s="1" t="n"/>
-    </row>
-    <row r="38" ht="33.55" customHeight="1">
-      <c r="C38" s="1" t="n"/>
-      <c r="E38" s="1" t="n"/>
-      <c r="G38" s="1" t="n"/>
-      <c r="I38" s="1" t="n"/>
-    </row>
-    <row r="39" ht="33.55" customHeight="1">
-      <c r="C39" s="1" t="n"/>
-      <c r="E39" s="1" t="n"/>
-      <c r="G39" s="1" t="n"/>
-      <c r="I39" s="1" t="n"/>
-    </row>
+    </row>
+    <row r="38" ht="33.55" customHeight="1"/>
+    <row r="39" ht="33.55" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="4294967293" verticalDpi="0"/>

--- a/统计信息.xlsx
+++ b/统计信息.xlsx
@@ -3295,11 +3295,11 @@
     </row>
     <row r="34" ht="33.55" customHeight="1">
       <c r="A34" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>大橘1号(暂用名)</t>
+          <t>白猫(暂用名)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3317,32 +3317,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>普通的大橘</t>
+          <t>普通的白猫</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>喜欢小只古典纹，毛色偏橘，从未被古典纹喜欢过，只会被被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2026年年初失踪。</t>
+          <t>和古典纹猫妈一起的白猫，2026年年初失踪。</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>big_orange_two</t>
+          <t>white_cat</t>
         </is>
       </c>
     </row>
     <row r="35" ht="33.55" customHeight="1">
       <c r="A35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>大橘2号（暂用名）</t>
+          <t>古典纹猫妈(暂用名)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -3355,27 +3355,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>普通的大橘</t>
+          <t>普通的狸花</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>有点偏奶油色，喜欢小只古典纹，古典纹也爱过，但是后来就被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2025年年末失踪。</t>
+          <t>大肚子怕人狸花，很像古典纹的放大版，只是左后腿多了一块纹，2026年年初失踪。</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>big_orange_three</t>
+          <t>gu_dian_wen_cat_mom</t>
         </is>
       </c>
     </row>
     <row r="36" ht="33.55" customHeight="1">
       <c r="A36" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>白猫(暂用名)</t>
+          <t>大橘1号(暂用名)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>普通的白猫</t>
+          <t>普通的大橘</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>和古典纹猫妈一起的白猫，2026年年初失踪。</t>
+          <t>喜欢小只古典纹，毛色偏橘，从未被古典纹喜欢过，只会被被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2026年年初失踪。</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>white_cat</t>
+          <t>big_orange_two</t>
         </is>
       </c>
     </row>
     <row r="37" ht="33.55" customHeight="1">
       <c r="A37" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>古典纹猫妈(暂用名)</t>
+          <t>大橘2号（暂用名）</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>普通的狸花</t>
+          <t>普通的大橘</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>大肚子怕人狸花，很像古典纹的放大版，只是左后腿多了一块纹，2026年年初失踪。</t>
+          <t>有点偏奶油色，喜欢小只古典纹，古典纹也爱过，但是后来就被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2025年年末失踪。</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>gu_dian_wen_cat_mom</t>
+          <t>big_orange_three</t>
         </is>
       </c>
     </row>

--- a/统计信息.xlsx
+++ b/统计信息.xlsx
@@ -2026,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="33.55" customHeight="1"/>
   <cols>
     <col width="16.28515625" customWidth="1" style="1" min="1" max="1"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>白手套口水巾(暂用名)</t>
+          <t>白手套口水巾1号(暂用名)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>黑老大</t>
+          <t>白手套口水巾2号(暂用名)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>五小只里最霸道的</t>
+          <t>五小只里面最早独立的</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>奶牛猫妈生的五小只里最霸道的，和他妈一样喜欢哈气，胸前有一个黑色的领结，特别霸道，特别护食。</t>
+          <t>奶牛猫妈生的五小只里最早就远走高飞的，和白手套口水巾1号相比丑一点，喜欢趴在电动车上。因为很早就不和他的兄弟们一起玩了，所以没有留下比较高清的照片。于2026年5月失踪。</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>black_boss</t>
+          <t>white_glove_bib_two</t>
         </is>
       </c>
     </row>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>五月</t>
+          <t>黑老大</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>五小只里最好看的</t>
+          <t>五小只里最霸道的</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>奶牛猫妈生的五小只里面最好看的一只，年纪轻轻就已怀孕，已绝育。</t>
+          <t>奶牛猫妈生的五小只里最霸道的，和他妈一样喜欢哈气，胸前有一个黑色的领结，特别霸道，特别护食。</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>black_boss</t>
         </is>
       </c>
     </row>
@@ -2691,16 +2691,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六月</t>
+          <t>五月</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2709,17 +2709,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>五小只里胆子最小的</t>
+          <t>五小只里最好看的</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>奶牛猫妈生的五小只里胆子最小的，别人都在吃东西，就他在最后面。</t>
+          <t>奶牛猫妈生的五小只里面最好看的一只，年纪轻轻就已怀孕，已绝育。</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>大脚橘</t>
+          <t>六月</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2747,17 +2747,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>贪吃的话痨</t>
+          <t>五小只里胆子最小的</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>突然出现在猫妈地盘里的一只话痨，喜欢被人摸下巴</t>
+          <t>奶牛猫妈生的五小只里胆子最小的，别人都在吃东西，就他在最后面。</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>big_foot_orange</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>贪吃哥</t>
+          <t>大脚橘</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2785,17 +2785,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>一直在蹭饭的路上</t>
+          <t>贪吃的话痨</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>在学校里转来转去，就为了蹭一口饭吃，是猫妈的垃圾桶。</t>
+          <t>突然出现在猫妈地盘里的一只话痨，喜欢被人摸下巴</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>like_eat_brother</t>
+          <t>big_foot_orange</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>头3</t>
+          <t>贪吃哥</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2823,17 +2823,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>猕猴桃</t>
+          <t>一直在蹭饭的路上</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>千里迢迢带着他的干女儿头孢来学校蹭饭，因为长得很像头套和黑头，所以取名叫头3。</t>
+          <t>在学校里转来转去，就为了蹭一口饭吃，是猫妈的垃圾桶。</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>head_three</t>
+          <t>like_eat_brother</t>
         </is>
       </c>
     </row>
@@ -2843,16 +2843,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>头孢</t>
+          <t>头3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2861,17 +2861,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>哈气就是喵喵</t>
+          <t>猕猴桃</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>千里迢迢跟着他的“干父亲”头3来学校蹭饭，因为他是头三的“干宝宝”，所以叫头孢（宝）。比较亲人，可以偷偷地摸，但是哈气和喵喵的代码写到了一起，哈气就是喵喵，喵喵就是哈气。</t>
+          <t>千里迢迢带着他的干女儿头孢来学校蹭饭，因为长得很像头套和黑头，所以取名叫头3。</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>tou_baby</t>
+          <t>head_three</t>
         </is>
       </c>
     </row>
@@ -2881,16 +2881,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>细细条</t>
+          <t>头孢</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>渣猫</t>
+          <t>哈气就是喵喵</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>特别标准的一只几把猫，和小咪草草都很要好。</t>
+          <t>千里迢迢跟着他的“干父亲”头3来学校蹭饭，因为他是头三的“干宝宝”，所以叫头孢（宝）。比较亲人，可以偷偷地摸，但是哈气和喵喵的代码写到了一起，哈气就是喵喵，喵喵就是哈气。</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>thin_stripe</t>
+          <t>tou_baby</t>
         </is>
       </c>
     </row>
@@ -2919,35 +2919,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>小黑</t>
+          <t>细细条</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>普通的玄猫</t>
+          <t>渣猫</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>仅仅两次出现过的黑猫</t>
+          <t>特别标准的一只几把猫，和小咪草草都很要好。</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>small_black</t>
+          <t>thin_stripe</t>
         </is>
       </c>
     </row>
@@ -2957,35 +2957,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>袁小花</t>
+          <t>小黑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>亲人的三花</t>
+          <t>普通的玄猫</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>突然出现的一只亲人的三花，不喜欢被人摸背和屁股。</t>
+          <t>仅仅两次出现过的黑猫</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>yuan_small_flower</t>
+          <t>small_black</t>
         </is>
       </c>
     </row>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>袁小牛</t>
+          <t>袁小花</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3013,17 +3013,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>貌美的奶牛</t>
+          <t>亲人的三花</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>突然出现的一只长得很像希特勒，但是眼睛很好看的奶牛，和小花是情侣。</t>
+          <t>突然出现的一只亲人的三花，不喜欢被人摸背和屁股。</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>yuan_small_cow</t>
+          <t>yuan_small_flower</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>点点</t>
+          <t>袁小牛</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>高精力和低精力并存</t>
+          <t>貌美的奶牛</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>突然出现的一只有橘色点点的小猫，高精力的时候特别贪玩，萎靡不振的时候在椅子上睁着眼睛睡觉。</t>
+          <t>突然出现的一只长得很像希特勒，但是眼睛很好看的奶牛，和小花是情侣。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>dot_dot</t>
+          <t>yuan_small_cow</t>
         </is>
       </c>
     </row>
@@ -3071,16 +3071,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>怕人三花(暂用名)</t>
+          <t>点点</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -3089,17 +3089,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>普通的三花</t>
+          <t>高精力和低精力并存</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>突然出现的一只怕人的三花，常常过来蹭饭。</t>
+          <t>突然出现的一只有橘色点点的小猫，高精力的时候特别贪玩，萎靡不振的时候在椅子上睁着眼睛睡觉。</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>pa_ren_san_hua</t>
+          <t>dot_dot</t>
         </is>
       </c>
     </row>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>狸花1号(暂用名)</t>
+          <t>怕人三花(暂用名)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3127,17 +3127,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>普通的狸花</t>
+          <t>普通的三花</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>一只普通的怕人狸花，背上有纹，有口水巾</t>
+          <t>突然出现的一只怕人的三花，常常过来蹭饭。</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>li_hua_one</t>
+          <t>pa_ren_san_hua</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>狸花2号(暂用名)</t>
+          <t>狸花1号(暂用名)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>一只普通的怕人狸花，看起来比较壮实，嘴巴比较白，经常蹭饭。</t>
+          <t>一只普通的怕人狸花，背上有纹，有口水巾</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>li_hua_two</t>
+          <t>li_hua_one</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>狸花3号(暂用名)</t>
+          <t>狸花2号(暂用名)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>一只普通的怕人小狸花，古典纹，前狸花帮的一员，2026年年初失踪</t>
+          <t>一只普通的怕人狸花，看起来比较壮实，嘴巴比较白，经常蹭饭。</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>li_hua_three</t>
+          <t>li_hua_two</t>
         </is>
       </c>
     </row>
@@ -3223,16 +3223,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>狸花4号(暂用名)</t>
+          <t>狸花3号(暂用名)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>一只普通的亲人狸花，以前陪伴小咪长大，眼屎很多，2025年9月失踪</t>
+          <t>一只普通的怕人小狸花，古典纹，前狸花帮的一员，2026年年初失踪</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>li_hua_four</t>
+          <t>li_hua_three</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>狸花5号(暂用名)</t>
+          <t>狸花4号(暂用名)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>一只尝尝到处蹭饭的狸花，2026年5月出现在校门口，喜欢蹭饭，和贪吃哥是好朋猫，是个gay</t>
+          <t>一只普通的亲人狸花，以前陪伴小咪长大，眼屎很多，2025年9月失踪</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>li_hua_five</t>
+          <t>li_hua_four</t>
         </is>
       </c>
     </row>
@@ -3299,16 +3299,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>白猫(暂用名)</t>
+          <t>狸花5号(暂用名)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3317,17 +3317,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>普通的白猫</t>
+          <t>普通的狸花</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>和古典纹猫妈一起的白猫，2026年年初失踪。</t>
+          <t>一只尝尝到处蹭饭的狸花，2026年5月出现在校门口，喜欢蹭饭，和贪吃哥是好朋猫，是个gay</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>white_cat</t>
+          <t>li_hua_five</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>古典纹猫妈(暂用名)</t>
+          <t>白猫(暂用名)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -3355,17 +3355,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>普通的狸花</t>
+          <t>普通的白猫</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>大肚子怕人狸花，很像古典纹的放大版，只是左后腿多了一块纹，2026年年初失踪。</t>
+          <t>和古典纹猫妈一起的白猫，2026年年初失踪。</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>gu_dian_wen_cat_mom</t>
+          <t>white_cat</t>
         </is>
       </c>
     </row>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>大橘1号(暂用名)</t>
+          <t>古典纹猫妈(暂用名)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -3393,17 +3393,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>普通的大橘</t>
+          <t>普通的狸花</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>喜欢小只古典纹，毛色偏橘，从未被古典纹喜欢过，只会被被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2026年年初失踪。</t>
+          <t>大肚子怕人狸花，很像古典纹的放大版，只是左后腿多了一块纹，2026年年初失踪。</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>big_orange_two</t>
+          <t>gu_dian_wen_cat_mom</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>大橘2号（暂用名）</t>
+          <t>大橘1号(暂用名)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3436,16 +3436,53 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>喜欢小只古典纹，毛色偏橘，从未被古典纹喜欢过，只会被被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2026年年初失踪。</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>big_orange_two</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="33.55" customHeight="1">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>大橘2号（暂用名）</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>普通的大橘</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>有点偏奶油色，喜欢小只古典纹，古典纹也爱过，但是后来就被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2025年年末失踪。</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>big_orange_three</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="33.55" customHeight="1"/>
     <row r="39" ht="33.55" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/统计信息.xlsx
+++ b/统计信息.xlsx
@@ -2026,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="33.55" customHeight="1"/>
   <cols>
     <col width="16.28515625" customWidth="1" style="1" min="1" max="1"/>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>河边奶牛(暂用名)</t>
+          <t>宕机猫(暂用名)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>蝙蝠侠</t>
+          <t>很像宕机猫</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>曾经住在河边桥底下的一只奶牛，像蝙蝠侠，2026年年初失踪</t>
+          <t>曾经住在河边桥底下的一只奶牛，像著名网图宕机猫，2026年年初失踪</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>喜欢小只古典纹，毛色偏橘，从未被古典纹喜欢过，只会被被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2026年年初失踪。</t>
+          <t>喜欢小只古典纹，毛色介于橘和奶油色中间，曾经被古典纹喜欢过，可是后来古典纹已经喜欢上了老橘，就不喜欢他了，明明是他先来的啊。</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3445,44 +3445,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="33.55" customHeight="1">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>大橘2号（暂用名）</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>普通的大橘</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>有点偏奶油色，喜欢小只古典纹，古典纹也爱过，但是后来就被古典纹哈气嫌弃，因为古典纹已经喜欢上了老橘，2025年年末失踪。</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>big_orange_three</t>
-        </is>
-      </c>
-    </row>
+    <row r="38" ht="33.55" customHeight="1"/>
     <row r="39" ht="33.55" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/统计信息.xlsx
+++ b/统计信息.xlsx
@@ -3413,12 +3413,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>大橘1号(暂用名)</t>
+          <t>竹马(暂用名)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>喜欢小只古典纹，毛色介于橘和奶油色中间，曾经被古典纹喜欢过，可是后来古典纹已经喜欢上了老橘，就不喜欢他了，明明是他先来的啊。</t>
+          <t>喜欢小只古典纹，毛色介于橘和奶油色中间，曾经被古典纹喜欢过，可是后来古典纹喜欢上了老橘，就不喜欢他了，明明是他先来的啊。</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>big_orange_two</t>
+          <t>big_orange_one</t>
         </is>
       </c>
     </row>

--- a/统计信息.xlsx
+++ b/统计信息.xlsx
@@ -2026,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="33.55" customHeight="1"/>
   <cols>
     <col width="16.28515625" customWidth="1" style="1" min="1" max="1"/>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>怕人的猫妈</t>
+          <t>可怜不幸的猫妈</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>黑老大</t>
+          <t>悍匪</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>奶牛猫妈生的五小只里最霸道的，和他妈一样喜欢哈气，胸前有一个黑色的领结，特别霸道，特别护食。</t>
+          <t>奶牛猫妈生的五小只里最霸道的，和他妈一样喜欢哈气，胸前有一个黑色的领结，是五小只的老大，特别护食。</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>渣猫</t>
+          <t>一只渣猫</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>特别标准的一只几把猫，和小咪草草都很要好。</t>
+          <t>特别标准的一只几把猫，喜欢过小咪、草草、瘦小古典纹。</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2957,35 +2957,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>小黑</t>
+          <t>袁小花</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>普通的玄猫</t>
+          <t>亲人的三花</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>仅仅两次出现过的黑猫</t>
+          <t>突然出现的一只亲人的三花，不喜欢被人摸背和屁股。</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>small_black</t>
+          <t>yuan_small_flower</t>
         </is>
       </c>
     </row>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>袁小花</t>
+          <t>袁小牛</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3013,17 +3013,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>亲人的三花</t>
+          <t>貌美的奶牛</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>突然出现的一只亲人的三花，不喜欢被人摸背和屁股。</t>
+          <t>突然出现的一只长得很像希特勒，但是眼睛很好看的奶牛，和小花是情侣。</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>yuan_small_flower</t>
+          <t>yuan_small_cow</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>袁小牛</t>
+          <t>点点</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>貌美的奶牛</t>
+          <t>高精力和低精力并存</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>突然出现的一只长得很像希特勒，但是眼睛很好看的奶牛，和小花是情侣。</t>
+          <t>突然出现的一只有橘色点点的小猫，高精力的时候特别贪玩，萎靡不振的时候在椅子上睁着眼睛睡觉。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>yuan_small_cow</t>
+          <t>dot_dot</t>
         </is>
       </c>
     </row>
@@ -3071,16 +3071,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>点点</t>
+          <t>怕人三花(暂用名)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -3089,17 +3089,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>高精力和低精力并存</t>
+          <t>普通的三花</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>突然出现的一只有橘色点点的小猫，高精力的时候特别贪玩，萎靡不振的时候在椅子上睁着眼睛睡觉。</t>
+          <t>突然出现的一只怕人的三花，常常过来蹭饭。</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>dot_dot</t>
+          <t>pa_ren_san_hua</t>
         </is>
       </c>
     </row>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>怕人三花(暂用名)</t>
+          <t>狸花1号(暂用名)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3127,17 +3127,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>普通的三花</t>
+          <t>普通的狸花</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>突然出现的一只怕人的三花，常常过来蹭饭。</t>
+          <t>一只普通的怕人狸花，背上有纹，有口水巾</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>pa_ren_san_hua</t>
+          <t>li_hua_one</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>狸花1号(暂用名)</t>
+          <t>狸花2号(暂用名)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>一只普通的怕人狸花，背上有纹，有口水巾</t>
+          <t>一只普通的怕人狸花，看起来比较壮实，嘴巴比较白，经常蹭饭。</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>li_hua_one</t>
+          <t>li_hua_two</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>狸花2号(暂用名)</t>
+          <t>狸花3号(暂用名)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>一只普通的怕人狸花，看起来比较壮实，嘴巴比较白，经常蹭饭。</t>
+          <t>一只普通的怕人小狸花，古典纹，前狸花帮的一员，2026年年初失踪</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>li_hua_two</t>
+          <t>li_hua_three</t>
         </is>
       </c>
     </row>
@@ -3223,16 +3223,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>狸花3号(暂用名)</t>
+          <t>狸花4号(暂用名)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>一只普通的怕人小狸花，古典纹，前狸花帮的一员，2026年年初失踪</t>
+          <t>一只普通的亲人狸花，以前陪伴小咪长大，眼屎很多，2025年9月失踪</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>li_hua_three</t>
+          <t>li_hua_four</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>狸花4号(暂用名)</t>
+          <t>狸花5号(暂用名)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>一只普通的亲人狸花，以前陪伴小咪长大，眼屎很多，2025年9月失踪</t>
+          <t>一只尝尝到处蹭饭的狸花，2026年5月出现在校门口，喜欢蹭饭，和贪吃哥是好朋猫，是个gay</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>li_hua_four</t>
+          <t>li_hua_five</t>
         </is>
       </c>
     </row>
@@ -3299,16 +3299,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>狸花5号(暂用名)</t>
+          <t>白猫(暂用名)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3317,17 +3317,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>普通的狸花</t>
+          <t>普通的白猫</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>一只尝尝到处蹭饭的狸花，2026年5月出现在校门口，喜欢蹭饭，和贪吃哥是好朋猫，是个gay</t>
+          <t>和古典纹猫妈一起的白猫，2026年年初失踪。</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>li_hua_five</t>
+          <t>white_cat</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>白猫(暂用名)</t>
+          <t>古典纹猫妈(暂用名)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -3355,17 +3355,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>普通的白猫</t>
+          <t>普通的狸花</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>和古典纹猫妈一起的白猫，2026年年初失踪。</t>
+          <t>大肚子怕人狸花，很像古典纹的放大版，只是左后腿多了一块纹，2026年年初失踪。</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>white_cat</t>
+          <t>gu_dian_wen_cat_mom</t>
         </is>
       </c>
     </row>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>古典纹猫妈(暂用名)</t>
+          <t>漂亮橘</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -3388,63 +3388,26 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>普通的狸花</t>
+          <t>漂亮的大橘</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>大肚子怕人狸花，很像古典纹的放大版，只是左后腿多了一块纹，2026年年初失踪。</t>
+          <t>喜欢小只古典纹，毛色介于橘和奶油色中间，曾经被古典纹喜欢过，可是后来古典纹喜欢上了老橘，就不喜欢他了，明明是他先来的啊。</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>gu_dian_wen_cat_mom</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="33.55" customHeight="1">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>竹马(暂用名)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>普通的大橘</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>喜欢小只古典纹，毛色介于橘和奶油色中间，曾经被古典纹喜欢过，可是后来古典纹喜欢上了老橘，就不喜欢他了，明明是他先来的啊。</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
           <t>big_orange_one</t>
         </is>
       </c>
     </row>
+    <row r="37" ht="33.55" customHeight="1"/>
     <row r="38" ht="33.55" customHeight="1"/>
     <row r="39" ht="33.55" customHeight="1"/>
   </sheetData>

--- a/统计信息.xlsx
+++ b/统计信息.xlsx
@@ -2027,7 +2027,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="33.55" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="33.55" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="16.28515625" customWidth="1" style="1" min="1" max="1"/>
     <col width="16.28515625" customWidth="1" style="2" min="2" max="2"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>校门口超级亲人的橘，经常在外卖车上睡觉，有很多人喂，于2025年年中失踪，小道消息是被领养了</t>
+          <t>校门口超级亲人的橘，经常在外卖桌子上睡觉，被很多人喜欢，于2025年年中失踪，小道消息是被领养了。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>小时候是一只怎么吃也吃不胖的高精力小猫，现在是吃一点点就胖的高精力小猫</t>
+          <t>小时候是一只怎么吃也吃不胖的高精力小猫，现在是吃一点点就胖的高精力小猫，喜欢到处探险惹事欺负小虫。</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>在学校里转来转去，就为了蹭一口饭吃，是猫妈的垃圾桶。</t>
+          <t>在学校里转来转去，就为了蹭一口饭吃，是猫妈的垃圾桶， 喜欢抢二头的饭。</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>一只尝尝到处蹭饭的狸花，2026年5月出现在校门口，喜欢蹭饭，和贪吃哥是好朋猫，是个gay</t>
+          <t>一只尝尝到处蹭饭的狸花，2026年5月出现在校门口，喜欢蹭饭，和贪吃哥是好朋猫，抢二头的地盘，是个gay</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">

--- a/统计信息.xlsx
+++ b/统计信息.xlsx
@@ -2027,7 +2027,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="33.55" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="33.55" customHeight="1"/>
   <cols>
     <col width="16.28515625" customWidth="1" style="1" min="1" max="1"/>
     <col width="16.28515625" customWidth="1" style="2" min="2" max="2"/>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>adopted</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/统计信息.xlsx
+++ b/统计信息.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Chart1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chart2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chart3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Chart4" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -156,13 +156,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
               <a:t>None</a:t>
             </a:r>
@@ -171,16 +171,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -240,10 +240,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:schemeClr val="accent1"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -403,8 +403,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -416,9 +416,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -454,7 +454,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -471,16 +471,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -509,10 +509,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -527,13 +527,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
               <a:t>None</a:t>
             </a:r>
@@ -542,16 +542,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -611,10 +611,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:schemeClr val="accent1"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -774,8 +774,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -787,9 +787,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -825,7 +825,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -842,16 +842,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -880,10 +880,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -898,13 +898,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
               <a:t>None</a:t>
             </a:r>
@@ -913,16 +913,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -982,10 +982,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:schemeClr val="accent1"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1145,8 +1145,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1158,9 +1158,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1196,7 +1196,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1213,16 +1213,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1251,10 +1251,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1269,13 +1269,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
               <a:t>None</a:t>
             </a:r>
@@ -1284,16 +1284,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -1353,10 +1353,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:schemeClr val="accent1"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1516,8 +1516,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1529,9 +1529,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1567,7 +1567,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1584,16 +1584,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1622,10 +1622,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1640,39 +1640,39 @@
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </chartsheet>
 </file>
 
 <file path=xl/chartsheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </chartsheet>
 </file>
 
 <file path=xl/chartsheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </chartsheet>
 </file>
 
 <file path=xl/chartsheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </chartsheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
     <pos x="0" y="0"/>
     <ext cx="0" cy="0"/>
@@ -1682,9 +1682,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1694,7 +1694,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
     <pos x="0" y="0"/>
     <ext cx="0" cy="0"/>
@@ -1704,9 +1704,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1716,7 +1716,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
     <pos x="0" y="0"/>
     <ext cx="0" cy="0"/>
@@ -1726,9 +1726,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1738,7 +1738,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
     <pos x="0" y="0"/>
     <ext cx="0" cy="0"/>
@@ -1748,9 +1748,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2027,7 +2027,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="33.55" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="33.55" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="16.28515625" customWidth="1" style="1" min="1" max="1"/>
     <col width="16.28515625" customWidth="1" style="2" min="2" max="2"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>校门口超级亲人的橘，经常在外卖桌子上睡觉，被很多人喜欢，于2025年年中失踪，小道消息是被领养了。</t>
+          <t>校门口超级亲人的橘。经常在外卖桌子上睡觉，见人就来蹭。已经被领养了。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>突然出现的一只亲人的三花，不喜欢被人摸背和屁股。</t>
+          <t>突然出现的一只亲人的三花，喜欢被人摸脸，不喜欢被人摸背和屁股。</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
